--- a/计算数据集(全).xlsx
+++ b/计算数据集(全).xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\Python\stelmor\code\math_sim\82A\v6（yang数据）\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\Python\stelmor\simulation_system\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2284F459-BDD2-4B3A-8D98-24CAA086C7E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F6B8766-8E3E-47F0-959C-650CDCEA4135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" calcOnSave="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1333,7 +1333,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1429,6 +1429,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="177" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -3680,122 +3698,122 @@
         <v>0.90668666666666664</v>
       </c>
     </row>
-    <row r="17" spans="1:39" x14ac:dyDescent="0.3">
-      <c r="A17" s="21" t="s">
+    <row r="17" spans="1:39" s="32" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="22">
+      <c r="C17" s="33">
         <v>0.82799999999999996</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="33">
         <v>0.21</v>
       </c>
-      <c r="E17" s="22">
+      <c r="E17" s="33">
         <v>0.51</v>
       </c>
-      <c r="F17" s="22">
+      <c r="F17" s="33">
         <v>1.4E-2</v>
       </c>
-      <c r="G17" s="22">
+      <c r="G17" s="33">
         <v>7.1000000000000004E-3</v>
       </c>
-      <c r="H17" s="22">
+      <c r="H17" s="33">
         <v>1.6E-2</v>
       </c>
-      <c r="I17" s="22">
+      <c r="I17" s="33">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="J17" s="22">
+      <c r="J17" s="33">
         <v>1.03E-2</v>
       </c>
-      <c r="K17" s="17">
+      <c r="K17" s="34">
         <v>897</v>
       </c>
-      <c r="L17" s="17">
+      <c r="L17" s="34">
         <v>0.83</v>
       </c>
-      <c r="M17" s="17">
+      <c r="M17" s="34">
         <v>0.88</v>
       </c>
-      <c r="N17" s="17">
+      <c r="N17" s="34">
         <v>0.97</v>
       </c>
-      <c r="O17" s="17">
+      <c r="O17" s="34">
         <v>1.08</v>
       </c>
-      <c r="P17" s="17">
+      <c r="P17" s="34">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Q17" s="17">
+      <c r="Q17" s="34">
         <v>1.1499999999999999</v>
       </c>
-      <c r="R17" s="17">
+      <c r="R17" s="34">
         <v>1.1599999999999999</v>
       </c>
-      <c r="S17" s="17">
+      <c r="S17" s="34">
         <v>1.1543000000000001</v>
       </c>
-      <c r="T17" s="17">
+      <c r="T17" s="34">
         <v>1.1517999999999999</v>
       </c>
-      <c r="U17" s="17">
+      <c r="U17" s="34">
         <v>1.1551</v>
       </c>
-      <c r="V17" s="23">
+      <c r="V17" s="35">
         <v>0</v>
       </c>
-      <c r="W17" s="23">
-        <v>99</v>
-      </c>
-      <c r="X17" s="23">
+      <c r="W17" s="35">
+        <v>99</v>
+      </c>
+      <c r="X17" s="35">
         <v>50</v>
       </c>
-      <c r="Y17" s="23">
+      <c r="Y17" s="35">
         <v>0</v>
       </c>
-      <c r="Z17" s="23">
+      <c r="Z17" s="35">
         <v>0</v>
       </c>
-      <c r="AA17" s="23">
+      <c r="AA17" s="35">
         <v>0</v>
       </c>
-      <c r="AB17" s="23">
+      <c r="AB17" s="35">
         <v>33</v>
       </c>
-      <c r="AC17" s="23">
+      <c r="AC17" s="35">
         <v>1012</v>
       </c>
-      <c r="AD17" s="6">
+      <c r="AD17" s="36">
         <v>11.324</v>
       </c>
-      <c r="AE17" s="6">
+      <c r="AE17" s="36">
         <v>0.16400000000000001</v>
       </c>
-      <c r="AF17" s="6">
+      <c r="AF17" s="36">
         <v>5.73</v>
       </c>
-      <c r="AG17" s="6">
+      <c r="AG17" s="36">
         <v>74.94</v>
       </c>
-      <c r="AH17" s="6">
+      <c r="AH17" s="36">
         <v>4.8217900000000001E-2</v>
       </c>
-      <c r="AI17" s="6">
+      <c r="AI17" s="36">
         <v>0.20719900000000002</v>
       </c>
-      <c r="AJ17" s="6">
+      <c r="AJ17" s="36">
         <v>0.47463</v>
       </c>
-      <c r="AK17" s="6" t="s">
+      <c r="AK17" s="36" t="s">
         <v>397</v>
       </c>
-      <c r="AL17" s="6">
+      <c r="AL17" s="36">
         <v>1.304</v>
       </c>
-      <c r="AM17" s="9">
+      <c r="AM17" s="37">
         <f t="shared" si="0"/>
         <v>0.91735333333333324</v>
       </c>
@@ -5360,122 +5378,122 @@
         <v>0.93208666666666673</v>
       </c>
     </row>
-    <row r="31" spans="1:39" x14ac:dyDescent="0.3">
-      <c r="A31" s="21" t="s">
+    <row r="31" spans="1:39" s="32" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="C31" s="22">
+      <c r="C31" s="33">
         <v>0.82799999999999996</v>
       </c>
-      <c r="D31" s="22">
+      <c r="D31" s="33">
         <v>0.21</v>
       </c>
-      <c r="E31" s="22">
+      <c r="E31" s="33">
         <v>0.51</v>
       </c>
-      <c r="F31" s="22">
+      <c r="F31" s="33">
         <v>1.4E-2</v>
       </c>
-      <c r="G31" s="22">
+      <c r="G31" s="33">
         <v>7.1000000000000004E-3</v>
       </c>
-      <c r="H31" s="22">
+      <c r="H31" s="33">
         <v>1.6E-2</v>
       </c>
-      <c r="I31" s="22">
+      <c r="I31" s="33">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="J31" s="22">
+      <c r="J31" s="33">
         <v>1.03E-2</v>
       </c>
-      <c r="K31" s="17">
+      <c r="K31" s="34">
         <v>910</v>
       </c>
-      <c r="L31" s="17">
+      <c r="L31" s="34">
         <v>0.82</v>
       </c>
-      <c r="M31" s="17">
+      <c r="M31" s="34">
         <v>0.88</v>
       </c>
-      <c r="N31" s="17">
+      <c r="N31" s="34">
         <v>0.97</v>
       </c>
-      <c r="O31" s="17">
+      <c r="O31" s="34">
         <v>1.08</v>
       </c>
-      <c r="P31" s="17">
+      <c r="P31" s="34">
         <v>1.1000000000000001</v>
       </c>
-      <c r="Q31" s="17">
+      <c r="Q31" s="34">
         <v>1.1499999999999999</v>
       </c>
-      <c r="R31" s="17">
+      <c r="R31" s="34">
         <v>1.1499999999999999</v>
       </c>
-      <c r="S31" s="17">
+      <c r="S31" s="34">
         <v>1.1575</v>
       </c>
-      <c r="T31" s="17">
+      <c r="T31" s="34">
         <v>1.1566000000000001</v>
       </c>
-      <c r="U31" s="17">
+      <c r="U31" s="34">
         <v>1.1552</v>
       </c>
-      <c r="V31" s="23">
+      <c r="V31" s="35">
         <v>0</v>
       </c>
-      <c r="W31" s="23">
-        <v>99</v>
-      </c>
-      <c r="X31" s="23">
+      <c r="W31" s="35">
+        <v>99</v>
+      </c>
+      <c r="X31" s="35">
         <v>50</v>
       </c>
-      <c r="Y31" s="23">
+      <c r="Y31" s="35">
         <v>0</v>
       </c>
-      <c r="Z31" s="23">
+      <c r="Z31" s="35">
         <v>0</v>
       </c>
-      <c r="AA31" s="23">
+      <c r="AA31" s="35">
         <v>0</v>
       </c>
-      <c r="AB31" s="23">
+      <c r="AB31" s="35">
         <v>38</v>
       </c>
-      <c r="AC31" s="23">
+      <c r="AC31" s="35">
         <v>1107</v>
       </c>
-      <c r="AD31" s="6">
+      <c r="AD31" s="36">
         <v>11.725</v>
       </c>
-      <c r="AE31" s="6">
+      <c r="AE31" s="36">
         <v>0.16200000000000001</v>
       </c>
-      <c r="AF31" s="6">
+      <c r="AF31" s="36">
         <v>5.67</v>
       </c>
-      <c r="AG31" s="6">
+      <c r="AG31" s="36">
         <v>76.45</v>
       </c>
-      <c r="AH31" s="6">
+      <c r="AH31" s="36">
         <v>4.8217900000000001E-2</v>
       </c>
-      <c r="AI31" s="6">
+      <c r="AI31" s="36">
         <v>0.20719900000000002</v>
       </c>
-      <c r="AJ31" s="6">
+      <c r="AJ31" s="36">
         <v>0.47463</v>
       </c>
-      <c r="AK31" s="6" t="s">
+      <c r="AK31" s="36" t="s">
         <v>397</v>
       </c>
-      <c r="AL31" s="6">
+      <c r="AL31" s="36">
         <v>1.2529999999999999</v>
       </c>
-      <c r="AM31" s="9">
+      <c r="AM31" s="37">
         <f t="shared" si="0"/>
         <v>0.91735333333333324</v>
       </c>
@@ -19520,122 +19538,122 @@
         <v>0.8998666666666667</v>
       </c>
     </row>
-    <row r="149" spans="1:39" x14ac:dyDescent="0.3">
-      <c r="A149" s="21" t="s">
+    <row r="149" spans="1:39" s="32" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="24" t="s">
         <v>296</v>
       </c>
-      <c r="B149" s="7" t="s">
+      <c r="B149" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C149" s="22">
+      <c r="C149" s="33">
         <v>0.83</v>
       </c>
-      <c r="D149" s="22">
+      <c r="D149" s="33">
         <v>0.21</v>
       </c>
-      <c r="E149" s="22">
+      <c r="E149" s="33">
         <v>0.53</v>
       </c>
-      <c r="F149" s="22">
+      <c r="F149" s="33">
         <v>1.0699999999999999E-2</v>
       </c>
-      <c r="G149" s="22">
+      <c r="G149" s="33">
         <v>8.2000000000000007E-3</v>
       </c>
-      <c r="H149" s="22">
+      <c r="H149" s="33">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="I149" s="22">
+      <c r="I149" s="33">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="J149" s="22">
+      <c r="J149" s="33">
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="K149" s="17">
+      <c r="K149" s="34">
         <v>856</v>
       </c>
-      <c r="L149" s="17">
+      <c r="L149" s="34">
         <v>1.1000000000000001</v>
       </c>
-      <c r="M149" s="17">
+      <c r="M149" s="34">
         <v>1.2</v>
       </c>
-      <c r="N149" s="17">
+      <c r="N149" s="34">
         <v>1.29</v>
       </c>
-      <c r="O149" s="17">
+      <c r="O149" s="34">
         <v>1.34</v>
       </c>
-      <c r="P149" s="17">
+      <c r="P149" s="34">
         <v>1.35</v>
       </c>
-      <c r="Q149" s="17">
+      <c r="Q149" s="34">
         <v>1.43</v>
       </c>
-      <c r="R149" s="17">
+      <c r="R149" s="34">
         <v>1.43</v>
       </c>
-      <c r="S149" s="17">
+      <c r="S149" s="34">
         <v>1.4237</v>
       </c>
-      <c r="T149" s="17">
+      <c r="T149" s="34">
         <v>1.4306000000000001</v>
       </c>
-      <c r="U149" s="17">
+      <c r="U149" s="34">
         <v>1.4751000000000001</v>
       </c>
-      <c r="V149" s="23">
-        <v>99</v>
-      </c>
-      <c r="W149" s="23">
-        <v>99</v>
-      </c>
-      <c r="X149" s="23">
+      <c r="V149" s="35">
+        <v>99</v>
+      </c>
+      <c r="W149" s="35">
+        <v>99</v>
+      </c>
+      <c r="X149" s="35">
         <v>95</v>
       </c>
-      <c r="Y149" s="23">
+      <c r="Y149" s="35">
         <v>95</v>
       </c>
-      <c r="Z149" s="23">
+      <c r="Z149" s="35">
         <v>90</v>
       </c>
-      <c r="AA149" s="23">
+      <c r="AA149" s="35">
         <v>85</v>
       </c>
-      <c r="AB149" s="23">
+      <c r="AB149" s="35">
         <v>39</v>
       </c>
-      <c r="AC149" s="23">
+      <c r="AC149" s="35">
         <v>1205</v>
       </c>
-      <c r="AD149" s="6">
+      <c r="AD149" s="36">
         <v>16.693000000000001</v>
       </c>
-      <c r="AE149" s="6">
+      <c r="AE149" s="36">
         <v>0.14699999999999999</v>
       </c>
-      <c r="AF149" s="6">
+      <c r="AF149" s="36">
         <v>5.14</v>
       </c>
-      <c r="AG149" s="6">
+      <c r="AG149" s="36">
         <v>89.71</v>
       </c>
-      <c r="AH149" s="6">
+      <c r="AH149" s="36">
         <v>4.8086999999999998E-2</v>
       </c>
-      <c r="AI149" s="6">
+      <c r="AI149" s="36">
         <v>0.21556900000000001</v>
       </c>
-      <c r="AJ149" s="6">
+      <c r="AJ149" s="36">
         <v>0.47463</v>
       </c>
-      <c r="AK149" s="6" t="s">
+      <c r="AK149" s="36" t="s">
         <v>397</v>
       </c>
-      <c r="AL149" s="6">
+      <c r="AL149" s="36">
         <v>0.749</v>
       </c>
-      <c r="AM149" s="9">
+      <c r="AM149" s="37">
         <f t="shared" si="2"/>
         <v>0.92181333333333337</v>
       </c>
@@ -22280,122 +22298,122 @@
         <v>0.9660266666666667</v>
       </c>
     </row>
-    <row r="172" spans="1:39" x14ac:dyDescent="0.3">
-      <c r="A172" s="21" t="s">
+    <row r="172" spans="1:39" s="32" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A172" s="24" t="s">
         <v>330</v>
       </c>
-      <c r="B172" s="25">
+      <c r="B172" s="38">
         <v>43929</v>
       </c>
-      <c r="C172" s="22">
+      <c r="C172" s="33">
         <v>0.86499999999999999</v>
       </c>
-      <c r="D172" s="22">
+      <c r="D172" s="33">
         <v>0.23</v>
       </c>
-      <c r="E172" s="22">
+      <c r="E172" s="33">
         <v>0.51</v>
       </c>
-      <c r="F172" s="22">
+      <c r="F172" s="33">
         <v>1.4E-2</v>
       </c>
-      <c r="G172" s="22">
+      <c r="G172" s="33">
         <v>5.7000000000000002E-3</v>
       </c>
-      <c r="H172" s="22">
+      <c r="H172" s="33">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="I172" s="22">
+      <c r="I172" s="33">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="J172" s="22">
+      <c r="J172" s="33">
         <v>9.7999999999999997E-3</v>
       </c>
-      <c r="K172" s="17">
+      <c r="K172" s="34">
         <v>898</v>
       </c>
-      <c r="L172" s="17">
+      <c r="L172" s="34">
         <v>0.99</v>
       </c>
-      <c r="M172" s="17">
+      <c r="M172" s="34">
         <v>1.08</v>
       </c>
-      <c r="N172" s="17">
+      <c r="N172" s="34">
         <v>1.1599999999999999</v>
       </c>
-      <c r="O172" s="17">
+      <c r="O172" s="34">
         <v>1.2</v>
       </c>
-      <c r="P172" s="17">
+      <c r="P172" s="34">
         <v>1.21</v>
       </c>
-      <c r="Q172" s="17">
+      <c r="Q172" s="34">
         <v>1.28</v>
       </c>
-      <c r="R172" s="17">
+      <c r="R172" s="34">
         <v>1.29</v>
       </c>
-      <c r="S172" s="17">
+      <c r="S172" s="34">
         <v>1.2841</v>
       </c>
-      <c r="T172" s="17">
+      <c r="T172" s="34">
         <v>1.2821</v>
       </c>
-      <c r="U172" s="17">
+      <c r="U172" s="34">
         <v>1.3526</v>
       </c>
-      <c r="V172" s="23">
+      <c r="V172" s="35">
         <v>0</v>
       </c>
-      <c r="W172" s="23">
-        <v>99</v>
-      </c>
-      <c r="X172" s="23">
-        <v>99</v>
-      </c>
-      <c r="Y172" s="23">
+      <c r="W172" s="35">
+        <v>99</v>
+      </c>
+      <c r="X172" s="35">
+        <v>99</v>
+      </c>
+      <c r="Y172" s="35">
         <v>80</v>
       </c>
-      <c r="Z172" s="23">
+      <c r="Z172" s="35">
         <v>60</v>
       </c>
-      <c r="AA172" s="23">
+      <c r="AA172" s="35">
         <v>50</v>
       </c>
-      <c r="AB172" s="23">
+      <c r="AB172" s="35">
         <v>36</v>
       </c>
-      <c r="AC172" s="23">
+      <c r="AC172" s="35">
         <v>1180</v>
       </c>
-      <c r="AD172" s="6">
+      <c r="AD172" s="36">
         <v>14.516999999999999</v>
       </c>
-      <c r="AE172" s="6">
+      <c r="AE172" s="36">
         <v>0.151</v>
       </c>
-      <c r="AF172" s="6">
+      <c r="AF172" s="36">
         <v>5.28</v>
       </c>
-      <c r="AG172" s="6">
+      <c r="AG172" s="36">
         <v>85.41</v>
       </c>
-      <c r="AH172" s="6">
+      <c r="AH172" s="36">
         <v>4.8199800000000001E-2</v>
       </c>
-      <c r="AI172" s="6">
+      <c r="AI172" s="36">
         <v>0.201737</v>
       </c>
-      <c r="AJ172" s="6">
+      <c r="AJ172" s="36">
         <v>0.52327900000000005</v>
       </c>
-      <c r="AK172" s="6" t="s">
+      <c r="AK172" s="36" t="s">
         <v>398</v>
       </c>
-      <c r="AL172" s="6">
+      <c r="AL172" s="36">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="AM172" s="9">
+      <c r="AM172" s="37">
         <f t="shared" si="2"/>
         <v>0.95551999999999992</v>
       </c>
@@ -29534,7 +29552,7 @@
         <v>0.23</v>
       </c>
       <c r="E234" s="2">
-        <f t="shared" ref="E234:AB234" si="4">MAX(E2:E231)</f>
+        <f t="shared" ref="E234:AA234" si="4">MAX(E2:E231)</f>
         <v>0.55000000000000004</v>
       </c>
       <c r="F234" s="2">
@@ -29639,111 +29657,111 @@
         <v>399</v>
       </c>
       <c r="C235" s="2">
-        <f>MIN(C2:C231)</f>
+        <f t="shared" ref="C235:AC235" si="5">MIN(C2:C231)</f>
         <v>0.81</v>
       </c>
       <c r="D235" s="2">
-        <f>MIN(D2:D231)</f>
+        <f t="shared" si="5"/>
         <v>0.18</v>
       </c>
       <c r="E235" s="2">
-        <f>MIN(E2:E231)</f>
+        <f t="shared" si="5"/>
         <v>0.47</v>
       </c>
       <c r="F235" s="2">
-        <f>MIN(F2:F231)</f>
+        <f t="shared" si="5"/>
         <v>6.1999999999999998E-3</v>
       </c>
       <c r="G235" s="2">
-        <f>MIN(G2:G231)</f>
+        <f t="shared" si="5"/>
         <v>2.5000000000000001E-3</v>
       </c>
       <c r="H235" s="2">
-        <f>MIN(H2:H231)</f>
+        <f t="shared" si="5"/>
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="I235" s="2">
-        <f>MIN(I2:I231)</f>
+        <f t="shared" si="5"/>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="J235" s="2">
-        <f>MIN(J2:J231)</f>
+        <f t="shared" si="5"/>
         <v>5.8999999999999999E-3</v>
       </c>
       <c r="K235" s="2">
-        <f>MIN(K2:K231)</f>
+        <f t="shared" si="5"/>
         <v>840</v>
       </c>
       <c r="L235" s="2">
-        <f>MIN(L2:L231)</f>
+        <f t="shared" si="5"/>
         <v>0.82</v>
       </c>
       <c r="M235" s="2">
-        <f>MIN(M2:M231)</f>
+        <f t="shared" si="5"/>
         <v>0.88</v>
       </c>
       <c r="N235" s="2">
-        <f>MIN(N2:N231)</f>
+        <f t="shared" si="5"/>
         <v>0.96</v>
       </c>
       <c r="O235" s="2">
-        <f>MIN(O2:O231)</f>
+        <f t="shared" si="5"/>
         <v>1.06</v>
       </c>
       <c r="P235" s="2">
-        <f>MIN(P2:P231)</f>
+        <f t="shared" si="5"/>
         <v>0.43</v>
       </c>
       <c r="Q235" s="2">
-        <f>MIN(Q2:Q231)</f>
+        <f t="shared" si="5"/>
         <v>0.43</v>
       </c>
       <c r="R235" s="2">
-        <f>MIN(R2:R231)</f>
+        <f t="shared" si="5"/>
         <v>0.43</v>
       </c>
       <c r="S235" s="2">
-        <f>MIN(S2:S231)</f>
+        <f t="shared" si="5"/>
         <v>0.43109999999999998</v>
       </c>
       <c r="T235" s="28">
-        <f>MIN(T2:T231)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U235" s="28">
-        <f>MIN(U2:U231)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="V235" s="2">
-        <f>MIN(V2:V231)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="W235" s="2">
-        <f>MIN(W2:W231)</f>
+        <f t="shared" si="5"/>
         <v>50</v>
       </c>
       <c r="X235" s="2">
-        <f>MIN(X2:X231)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Y235" s="2">
-        <f>MIN(Y2:Y231)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Z235" s="2">
-        <f>MIN(Z2:Z231)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AA235" s="2">
-        <f>MIN(AA2:AA231)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB235" s="2">
-        <f>MIN(AB2:AB231)</f>
+        <f t="shared" si="5"/>
         <v>31</v>
       </c>
       <c r="AC235" s="2">
-        <f>MIN(AC2:AC231)</f>
+        <f t="shared" si="5"/>
         <v>964</v>
       </c>
     </row>
